--- a/V2/product/ibor/data/look-through/lookthrough_data.xlsx
+++ b/V2/product/ibor/data/look-through/lookthrough_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AndrewPoulter\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/steve/work/code/notebooks/public/V2/product/ibor/data/look-through/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE33215-F025-4C51-8363-D3E1CEAE9E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEE75BD-D02F-5342-AC3C-9AA2DA770B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{140D0F4F-AA5F-4E16-95A8-8F9F58C5F424}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{140D0F4F-AA5F-4E16-95A8-8F9F58C5F424}"/>
   </bookViews>
   <sheets>
     <sheet name="transactions" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="market_prices" sheetId="4" r:id="rId3"/>
     <sheet name="instruments" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -524,9 +524,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,6 +543,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -567,9 +574,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,6 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{23AC1E74-AB5B-4998-A2CE-192F17EFC4A4}"/>
@@ -599,9 +607,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -639,7 +647,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -745,7 +753,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -887,7 +895,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -896,23 +904,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E4483A-D81C-486B-9469-6BB1913F7014}">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.85546875" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>90</v>
       </c>
@@ -950,7 +958,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -985,7 +993,7 @@
         <v>291800</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1020,7 +1028,7 @@
         <v>89815</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>95</v>
       </c>
@@ -1055,7 +1063,7 @@
         <v>90037.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -1090,7 +1098,7 @@
         <v>746999</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -1125,7 +1133,7 @@
         <v>1300000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>98</v>
       </c>
@@ -1160,7 +1168,7 @@
         <v>145050</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -1195,7 +1203,7 @@
         <v>49364.999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -1230,7 +1238,7 @@
         <v>363480</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>101</v>
       </c>
@@ -1265,7 +1273,7 @@
         <v>32840</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -1300,7 +1308,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -1335,7 +1343,7 @@
         <v>41967.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>104</v>
       </c>
@@ -1370,7 +1378,7 @@
         <v>64250</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>105</v>
       </c>
@@ -1405,7 +1413,7 @@
         <v>40733</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -1440,7 +1448,7 @@
         <v>686100</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -1475,7 +1483,7 @@
         <v>3955.0000000000005</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>120</v>
       </c>
@@ -1510,7 +1518,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -1545,7 +1553,7 @@
         <v>5975</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>151</v>
       </c>
@@ -1580,7 +1588,7 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -1615,7 +1623,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>153</v>
       </c>
@@ -1650,7 +1658,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>156</v>
       </c>
@@ -1698,16 +1706,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84DB2B2-D7B3-4F14-9CA4-CF7C421E0851}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1724,7 +1732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
@@ -1741,7 +1749,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>108</v>
       </c>
@@ -1758,7 +1766,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>108</v>
       </c>
@@ -1775,7 +1783,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>108</v>
       </c>
@@ -1792,7 +1800,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -1809,7 +1817,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>108</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>108</v>
       </c>
@@ -1843,7 +1851,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>108</v>
       </c>
@@ -1860,7 +1868,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>108</v>
       </c>
@@ -1877,7 +1885,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>108</v>
       </c>
@@ -1904,16 +1912,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E615609-E297-47FD-9AAE-07E524F332F5}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1938,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
@@ -1947,7 +1955,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>108</v>
       </c>
@@ -1964,7 +1972,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>108</v>
       </c>
@@ -1981,7 +1989,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>108</v>
       </c>
@@ -1998,7 +2006,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -2015,7 +2023,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>108</v>
       </c>
@@ -2032,279 +2040,279 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>111</v>
       </c>
       <c r="D8">
-        <v>1150</v>
+        <v>293</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>111</v>
       </c>
       <c r="D9">
-        <v>293</v>
+        <v>591</v>
       </c>
       <c r="E9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>111</v>
       </c>
       <c r="D10">
-        <v>591</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>111</v>
       </c>
       <c r="D11">
-        <v>337</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>111</v>
       </c>
       <c r="D12">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>111</v>
       </c>
       <c r="D13">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>111</v>
       </c>
       <c r="D14">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
         <v>111</v>
       </c>
       <c r="D15">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>111</v>
       </c>
       <c r="D16">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>111</v>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
         <v>111</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
         <v>111</v>
       </c>
       <c r="D19">
-        <v>168</v>
+        <v>407</v>
       </c>
       <c r="E19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>111</v>
       </c>
       <c r="D20">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
         <v>111</v>
       </c>
       <c r="D21">
-        <v>407</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B22" t="s">
-        <v>85</v>
+      <c r="B22" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C22" t="s">
         <v>111</v>
       </c>
       <c r="D22">
-        <v>137</v>
+        <v>387.7</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B23" t="s">
-        <v>84</v>
+      <c r="B23" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C23" t="s">
         <v>111</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>599</v>
       </c>
       <c r="E23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
@@ -2321,7 +2329,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>108</v>
       </c>
@@ -2338,7 +2346,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
@@ -2355,7 +2363,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>108</v>
       </c>
@@ -2372,7 +2380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>108</v>
       </c>
@@ -2389,7 +2397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>108</v>
       </c>
@@ -2414,19 +2422,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE77CEC-E9ED-4D7C-87C7-6AFD98461E9D}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2452,7 +2460,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2475,7 +2483,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2498,7 +2506,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2521,7 +2529,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2567,7 +2575,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -2590,7 +2598,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2613,7 +2621,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -2636,7 +2644,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2659,7 +2667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2682,7 +2690,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -2705,7 +2713,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -2728,7 +2736,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -2751,7 +2759,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -2774,7 +2782,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -2797,7 +2805,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -2820,7 +2828,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -2843,7 +2851,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -2866,7 +2874,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -2889,7 +2897,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -2912,7 +2920,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2935,7 +2943,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2958,7 +2966,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -2981,7 +2989,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>133</v>
       </c>
@@ -3004,7 +3012,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>134</v>
       </c>
@@ -3027,7 +3035,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>135</v>
       </c>
@@ -3050,7 +3058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>157</v>
       </c>
